--- a/Cartón médico.xlsx
+++ b/Cartón médico.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julieta\Desktop\carton medico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcc_0\tesis\carton-medico-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285B65B8-EB5B-4568-9B8B-24CAF9C58A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46BB4B7-CDFA-4399-984C-B49A138217E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D61D5309-C93C-475C-AC6F-20B430C251E0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D61D5309-C93C-475C-AC6F-20B430C251E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Frente" sheetId="1" r:id="rId1"/>
@@ -40,17 +40,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="63">
   <si>
     <t>1. Datos del paciente</t>
   </si>
   <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Apellido</t>
-  </si>
-  <si>
     <t>Edad</t>
   </si>
   <si>
@@ -232,6 +226,9 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>Apellido y Nombre</t>
   </si>
 </sst>
 </file>
@@ -364,7 +361,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="55">
+  <borders count="59">
     <border>
       <left/>
       <right/>
@@ -1058,11 +1055,55 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1224,6 +1265,174 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1239,128 +1448,35 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1368,6 +1484,12 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1404,98 +1526,29 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1976,21 +2029,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:J40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.77734375" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" customWidth="1"/>
-    <col min="3" max="4" width="8.6640625" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" customWidth="1"/>
-    <col min="6" max="6" width="2.77734375" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" customWidth="1"/>
-    <col min="8" max="8" width="10.109375" customWidth="1"/>
-    <col min="9" max="9" width="1.109375" customWidth="1"/>
-    <col min="10" max="10" width="22.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.81640625" customWidth="1"/>
+    <col min="2" max="2" width="15.81640625" customWidth="1"/>
+    <col min="3" max="4" width="8.6328125" customWidth="1"/>
+    <col min="5" max="5" width="5.54296875" customWidth="1"/>
+    <col min="6" max="6" width="2.81640625" customWidth="1"/>
+    <col min="7" max="7" width="8.6328125" customWidth="1"/>
+    <col min="8" max="8" width="10.08984375" customWidth="1"/>
+    <col min="9" max="9" width="1.08984375" customWidth="1"/>
+    <col min="10" max="10" width="22.1796875" customWidth="1"/>
     <col min="11" max="11" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B1" s="13"/>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2001,46 +2054,46 @@
       <c r="I1" s="10"/>
       <c r="J1" s="8"/>
     </row>
-    <row r="2" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B2" s="14"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="108" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
+      <c r="D2" s="85" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B3" s="14"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="109" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="109"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="109"/>
+      <c r="D3" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
       <c r="I3" s="5"/>
       <c r="J3" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B4" s="14"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="121" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
+      <c r="D4" s="105" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="2:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B5" s="15"/>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
@@ -2051,7 +2104,7 @@
       <c r="I5" s="18"/>
       <c r="J5" s="7"/>
     </row>
-    <row r="7" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>0</v>
       </c>
@@ -2060,257 +2113,255 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="72" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="95"/>
+    <row r="8" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B9" s="168" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="170"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="172"/>
       <c r="G9" s="19"/>
       <c r="H9" s="72" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="91"/>
-      <c r="J9" s="92"/>
-    </row>
-    <row r="10" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="97"/>
+      <c r="I9" s="123"/>
+      <c r="J9" s="124"/>
+    </row>
+    <row r="10" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B10" s="169"/>
+      <c r="C10" s="173"/>
+      <c r="D10" s="174"/>
+      <c r="E10" s="174"/>
+      <c r="F10" s="175"/>
       <c r="G10" s="19"/>
       <c r="H10" s="71" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="101"/>
-      <c r="J10" s="102"/>
-    </row>
-    <row r="11" spans="2:10" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="I10" s="130"/>
+      <c r="J10" s="131"/>
+    </row>
+    <row r="11" spans="2:10" ht="16.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="73" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="I11" s="104"/>
-      <c r="J11" s="105"/>
-    </row>
-    <row r="12" spans="2:10" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="125" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" s="133"/>
+      <c r="J11" s="134"/>
+    </row>
+    <row r="12" spans="2:10" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="2"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="100"/>
-      <c r="F12" s="100"/>
-      <c r="G12" s="103"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="106"/>
-      <c r="J12" s="107"/>
-    </row>
-    <row r="13" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C12" s="129"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="132"/>
+      <c r="H12" s="126"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="136"/>
+    </row>
+    <row r="13" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B14" s="72" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="122"/>
-      <c r="D14" s="123"/>
-      <c r="E14" s="123"/>
-      <c r="F14" s="123"/>
-      <c r="G14" s="123"/>
-      <c r="H14" s="123"/>
-      <c r="I14" s="123"/>
-      <c r="J14" s="124"/>
-    </row>
-    <row r="15" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="C14" s="106"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="107"/>
+      <c r="F14" s="107"/>
+      <c r="G14" s="107"/>
+      <c r="H14" s="107"/>
+      <c r="I14" s="107"/>
+      <c r="J14" s="108"/>
+    </row>
+    <row r="15" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B15" s="71" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="93" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="94"/>
+      <c r="G15" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="85" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="110"/>
-      <c r="G15" s="85" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="86"/>
-      <c r="I15" s="86"/>
-      <c r="J15" s="87"/>
-    </row>
-    <row r="16" spans="2:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H15" s="109"/>
+      <c r="I15" s="109"/>
+      <c r="J15" s="110"/>
+    </row>
+    <row r="16" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="74" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="88"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="89"/>
-      <c r="F16" s="89"/>
-      <c r="G16" s="89"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="89"/>
-      <c r="J16" s="90"/>
-    </row>
-    <row r="17" spans="2:10" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="82" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="148"/>
-      <c r="D17" s="149"/>
-      <c r="E17" s="149"/>
-      <c r="F17" s="149"/>
-      <c r="G17" s="149"/>
-      <c r="H17" s="149"/>
-      <c r="I17" s="149"/>
-      <c r="J17" s="150"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="83"/>
-      <c r="C18" s="151"/>
-      <c r="D18" s="152"/>
-      <c r="E18" s="152"/>
-      <c r="F18" s="152"/>
-      <c r="G18" s="152"/>
-      <c r="H18" s="152"/>
-      <c r="I18" s="152"/>
-      <c r="J18" s="153"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="83"/>
-      <c r="C19" s="151"/>
-      <c r="D19" s="152"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="152"/>
-      <c r="G19" s="152"/>
-      <c r="H19" s="152"/>
-      <c r="I19" s="152"/>
-      <c r="J19" s="153"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="83"/>
-      <c r="C20" s="151"/>
-      <c r="D20" s="152"/>
-      <c r="E20" s="152"/>
-      <c r="F20" s="152"/>
-      <c r="G20" s="152"/>
-      <c r="H20" s="152"/>
-      <c r="I20" s="152"/>
-      <c r="J20" s="153"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="83"/>
-      <c r="C21" s="151"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="152"/>
-      <c r="I21" s="152"/>
-      <c r="J21" s="153"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="83"/>
-      <c r="C22" s="151"/>
-      <c r="D22" s="152"/>
-      <c r="E22" s="152"/>
-      <c r="F22" s="152"/>
-      <c r="G22" s="152"/>
-      <c r="H22" s="152"/>
-      <c r="I22" s="152"/>
-      <c r="J22" s="153"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="83"/>
-      <c r="C23" s="151"/>
-      <c r="D23" s="152"/>
-      <c r="E23" s="152"/>
-      <c r="F23" s="152"/>
-      <c r="G23" s="152"/>
-      <c r="H23" s="152"/>
-      <c r="I23" s="152"/>
-      <c r="J23" s="153"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="83"/>
-      <c r="C24" s="151"/>
-      <c r="D24" s="152"/>
-      <c r="E24" s="152"/>
-      <c r="F24" s="152"/>
-      <c r="G24" s="152"/>
-      <c r="H24" s="152"/>
-      <c r="I24" s="152"/>
-      <c r="J24" s="153"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="83"/>
-      <c r="C25" s="151"/>
-      <c r="D25" s="152"/>
-      <c r="E25" s="152"/>
-      <c r="F25" s="152"/>
-      <c r="G25" s="152"/>
-      <c r="H25" s="152"/>
-      <c r="I25" s="152"/>
-      <c r="J25" s="153"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="83"/>
-      <c r="C26" s="151"/>
-      <c r="D26" s="152"/>
-      <c r="E26" s="152"/>
-      <c r="F26" s="152"/>
-      <c r="G26" s="152"/>
-      <c r="H26" s="152"/>
-      <c r="I26" s="152"/>
-      <c r="J26" s="153"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="83"/>
-      <c r="C27" s="151"/>
-      <c r="D27" s="152"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="152"/>
-      <c r="G27" s="152"/>
-      <c r="H27" s="152"/>
-      <c r="I27" s="152"/>
-      <c r="J27" s="153"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="83"/>
-      <c r="C28" s="151"/>
-      <c r="D28" s="152"/>
-      <c r="E28" s="152"/>
-      <c r="F28" s="152"/>
-      <c r="G28" s="152"/>
-      <c r="H28" s="152"/>
-      <c r="I28" s="152"/>
-      <c r="J28" s="153"/>
-    </row>
-    <row r="29" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="84"/>
-      <c r="C29" s="154"/>
-      <c r="D29" s="155"/>
-      <c r="E29" s="155"/>
-      <c r="F29" s="155"/>
-      <c r="G29" s="155"/>
-      <c r="H29" s="155"/>
-      <c r="I29" s="155"/>
-      <c r="J29" s="156"/>
-    </row>
-    <row r="30" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+      <c r="C16" s="111"/>
+      <c r="D16" s="112"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="112"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="112"/>
+      <c r="J16" s="113"/>
+    </row>
+    <row r="17" spans="2:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="140" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="114"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="116"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B18" s="141"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="118"/>
+      <c r="I18" s="118"/>
+      <c r="J18" s="119"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B19" s="141"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="118"/>
+      <c r="H19" s="118"/>
+      <c r="I19" s="118"/>
+      <c r="J19" s="119"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B20" s="141"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="118"/>
+      <c r="H20" s="118"/>
+      <c r="I20" s="118"/>
+      <c r="J20" s="119"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B21" s="141"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="118"/>
+      <c r="H21" s="118"/>
+      <c r="I21" s="118"/>
+      <c r="J21" s="119"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B22" s="141"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="118"/>
+      <c r="H22" s="118"/>
+      <c r="I22" s="118"/>
+      <c r="J22" s="119"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B23" s="141"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="118"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="119"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B24" s="141"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="118"/>
+      <c r="H24" s="118"/>
+      <c r="I24" s="118"/>
+      <c r="J24" s="119"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B25" s="141"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="118"/>
+      <c r="G25" s="118"/>
+      <c r="H25" s="118"/>
+      <c r="I25" s="118"/>
+      <c r="J25" s="119"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B26" s="141"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="118"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="118"/>
+      <c r="H26" s="118"/>
+      <c r="I26" s="118"/>
+      <c r="J26" s="119"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B27" s="141"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="118"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="118"/>
+      <c r="G27" s="118"/>
+      <c r="H27" s="118"/>
+      <c r="I27" s="118"/>
+      <c r="J27" s="119"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B28" s="141"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="118"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="118"/>
+      <c r="G28" s="118"/>
+      <c r="H28" s="118"/>
+      <c r="I28" s="118"/>
+      <c r="J28" s="119"/>
+    </row>
+    <row r="29" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="126"/>
+      <c r="C29" s="120"/>
+      <c r="D29" s="121"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="121"/>
+      <c r="H29" s="121"/>
+      <c r="I29" s="121"/>
+      <c r="J29" s="122"/>
+    </row>
+    <row r="30" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
       <c r="E30" s="23"/>
@@ -2320,118 +2371,135 @@
       <c r="I30" s="23"/>
       <c r="J30" s="23"/>
     </row>
-    <row r="31" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B32" s="3"/>
       <c r="C32" s="18"/>
       <c r="D32" s="18"/>
     </row>
-    <row r="33" spans="2:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B33" s="75" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="114" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33" s="115"/>
+        <v>53</v>
+      </c>
+      <c r="C33" s="98" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="99"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="116" t="s">
-        <v>38</v>
-      </c>
-      <c r="G33" s="117"/>
-      <c r="H33" s="79"/>
-      <c r="I33" s="80"/>
-      <c r="J33" s="81"/>
-    </row>
-    <row r="34" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="35" spans="2:10" ht="31.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F33" s="100" t="s">
+        <v>36</v>
+      </c>
+      <c r="G33" s="101"/>
+      <c r="H33" s="137"/>
+      <c r="I33" s="138"/>
+      <c r="J33" s="139"/>
+    </row>
+    <row r="34" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="35" spans="2:10" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="9"/>
-      <c r="C35" s="111" t="s">
+      <c r="C35" s="95" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="96"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="102" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="103"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="104"/>
+      <c r="J35" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D35" s="112"/>
-      <c r="E35" s="113"/>
-      <c r="F35" s="118" t="s">
+    </row>
+    <row r="36" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B36" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="G35" s="119"/>
-      <c r="H35" s="119"/>
-      <c r="I35" s="120"/>
-      <c r="J35" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B36" s="66" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="160"/>
-      <c r="D36" s="161"/>
-      <c r="E36" s="162"/>
-      <c r="F36" s="160"/>
-      <c r="G36" s="161"/>
-      <c r="H36" s="161"/>
-      <c r="I36" s="162"/>
-      <c r="J36" s="163"/>
-    </row>
-    <row r="37" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C36" s="90"/>
+      <c r="D36" s="91"/>
+      <c r="E36" s="92"/>
+      <c r="F36" s="90"/>
+      <c r="G36" s="91"/>
+      <c r="H36" s="91"/>
+      <c r="I36" s="92"/>
+      <c r="J36" s="79"/>
+    </row>
+    <row r="37" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B37" s="67" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="90"/>
+      <c r="D37" s="91"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="90"/>
+      <c r="G37" s="91"/>
+      <c r="H37" s="91"/>
+      <c r="I37" s="92"/>
+      <c r="J37" s="80"/>
+    </row>
+    <row r="38" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B38" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="160"/>
-      <c r="D37" s="161"/>
-      <c r="E37" s="162"/>
-      <c r="F37" s="160"/>
-      <c r="G37" s="161"/>
-      <c r="H37" s="161"/>
-      <c r="I37" s="162"/>
-      <c r="J37" s="164"/>
-    </row>
-    <row r="38" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B38" s="68" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="160"/>
-      <c r="D38" s="161"/>
-      <c r="E38" s="162"/>
-      <c r="F38" s="160"/>
-      <c r="G38" s="161"/>
-      <c r="H38" s="161"/>
-      <c r="I38" s="162"/>
-      <c r="J38" s="164"/>
-    </row>
-    <row r="39" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C38" s="90"/>
+      <c r="D38" s="91"/>
+      <c r="E38" s="92"/>
+      <c r="F38" s="90"/>
+      <c r="G38" s="91"/>
+      <c r="H38" s="91"/>
+      <c r="I38" s="92"/>
+      <c r="J38" s="80"/>
+    </row>
+    <row r="39" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B39" s="69" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="157"/>
-      <c r="D39" s="158"/>
-      <c r="E39" s="159"/>
-      <c r="F39" s="160"/>
-      <c r="G39" s="161"/>
-      <c r="H39" s="161"/>
-      <c r="I39" s="162"/>
-      <c r="J39" s="163"/>
-    </row>
-    <row r="40" spans="2:10" ht="31.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="C39" s="142"/>
+      <c r="D39" s="143"/>
+      <c r="E39" s="144"/>
+      <c r="F39" s="90"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="91"/>
+      <c r="I39" s="92"/>
+      <c r="J39" s="79"/>
+    </row>
+    <row r="40" spans="2:10" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="70" t="s">
-        <v>15</v>
-      </c>
-      <c r="C40" s="169"/>
-      <c r="D40" s="170"/>
-      <c r="E40" s="171"/>
-      <c r="F40" s="165"/>
-      <c r="G40" s="166"/>
-      <c r="H40" s="166"/>
-      <c r="I40" s="167"/>
-      <c r="J40" s="168"/>
+        <v>13</v>
+      </c>
+      <c r="C40" s="87"/>
+      <c r="D40" s="88"/>
+      <c r="E40" s="89"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="83"/>
+      <c r="I40" s="84"/>
+      <c r="J40" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:F10"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="C17:J29"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="I11:J12"/>
     <mergeCell ref="F40:I40"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="D3:H3"/>
@@ -2448,23 +2516,6 @@
     <mergeCell ref="F37:I37"/>
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="C14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="C17:J29"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="I11:J12"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="B17:B29"/>
-    <mergeCell ref="C39:E39"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.3" footer="0.3"/>
@@ -2479,15 +2530,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" customWidth="1"/>
-    <col min="3" max="6" width="20.88671875" customWidth="1"/>
-    <col min="7" max="10" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" customWidth="1"/>
+    <col min="3" max="6" width="20.90625" customWidth="1"/>
+    <col min="7" max="10" width="10.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="13"/>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -2495,35 +2546,35 @@
       <c r="E1" s="10"/>
       <c r="F1" s="8"/>
     </row>
-    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="14"/>
-      <c r="C2" s="108" t="s">
+      <c r="C2" s="85" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="85"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="14"/>
+      <c r="C3" s="112" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="112"/>
+      <c r="E3" s="145" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="146"/>
+    </row>
+    <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="14"/>
+      <c r="C4" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="108"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="C3" s="89" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" s="89"/>
-      <c r="E3" s="139" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="140"/>
-    </row>
-    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="C4" s="121" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="15"/>
       <c r="B5" s="18"/>
       <c r="C5" s="16"/>
@@ -2531,308 +2582,308 @@
       <c r="E5" s="18"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:6" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="146" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="147"/>
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="7" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="154" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="155"/>
       <c r="C7" s="76" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="77" t="s">
+      <c r="F7" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="77" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="78" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="125" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="126"/>
+    </row>
+    <row r="8" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="152" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="153"/>
       <c r="C8" s="31"/>
       <c r="D8" s="32"/>
       <c r="E8" s="32"/>
       <c r="F8" s="33"/>
     </row>
-    <row r="9" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="141" t="s">
-        <v>35</v>
+    <row r="9" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="147" t="s">
+        <v>33</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E9" s="47" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F9" s="48" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="142"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="148"/>
       <c r="B10" s="11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D10" s="50" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E10" s="50" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="32.549999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="132"/>
+    </row>
+    <row r="11" spans="1:6" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="160" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="161"/>
       <c r="C11" s="34"/>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
       <c r="F11" s="36"/>
     </row>
-    <row r="12" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="129" t="s">
+    <row r="12" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="158" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="48" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="159"/>
+      <c r="B13" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="C13" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="51" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="164" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="48" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="130"/>
-      <c r="B13" s="11" t="s">
+      <c r="C14" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="165"/>
+      <c r="B15" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="40" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="166" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="167"/>
+      <c r="C16" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="149" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="51" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="135" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="24" t="s">
+      <c r="B17" s="162" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="54" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="150"/>
+      <c r="B18" s="163"/>
+      <c r="C18" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" s="57" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="150"/>
+      <c r="B19" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="60" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="60" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="61" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="150"/>
+      <c r="B20" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="150"/>
+      <c r="B21" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="151"/>
+      <c r="B22" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" s="30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="152" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="27" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="136"/>
-      <c r="B15" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="40" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="137" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="138"/>
-      <c r="C16" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="143" t="s">
+      <c r="B23" s="153"/>
+      <c r="C23" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="45" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="156" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="133" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="52" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="54" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="144"/>
-      <c r="B18" s="134"/>
-      <c r="C18" s="55" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="56" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="56" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="57" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="144"/>
-      <c r="B19" s="58" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="59" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="61" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="144"/>
-      <c r="B20" s="62" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="51" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="144"/>
-      <c r="B21" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="145"/>
-      <c r="B22" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22" s="30" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="125" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="126"/>
-      <c r="C23" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="F23" s="45" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="128"/>
+      <c r="B24" s="157"/>
       <c r="C24" s="63"/>
       <c r="D24" s="64"/>
       <c r="E24" s="64"/>
@@ -2840,6 +2891,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
@@ -2848,13 +2906,6 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Cartón médico.xlsx
+++ b/Cartón médico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcc_0\tesis\carton-medico-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46BB4B7-CDFA-4399-984C-B49A138217E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D52A5D-4C12-455F-8699-50811AC4557B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D61D5309-C93C-475C-AC6F-20B430C251E0}"/>
   </bookViews>
@@ -1253,7 +1253,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1268,6 +1267,150 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1292,18 +1435,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1349,113 +1480,47 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1478,76 +1543,13 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2057,25 +2059,25 @@
     <row r="2" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B2" s="14"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="85" t="s">
+      <c r="D2" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
       <c r="J2" s="6"/>
     </row>
     <row r="3" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B3" s="14"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
+      <c r="E3" s="133"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="133"/>
+      <c r="H3" s="133"/>
       <c r="I3" s="5"/>
       <c r="J3" s="21" t="s">
         <v>57</v>
@@ -2084,13 +2086,13 @@
     <row r="4" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B4" s="14"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="105" t="s">
+      <c r="D4" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
       <c r="J4" s="6"/>
     </row>
     <row r="5" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
@@ -2115,72 +2117,72 @@
     </row>
     <row r="8" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="9" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B9" s="168" t="s">
+      <c r="B9" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="170"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="85"/>
       <c r="G9" s="19"/>
       <c r="H9" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="I9" s="123"/>
-      <c r="J9" s="124"/>
+      <c r="I9" s="116"/>
+      <c r="J9" s="117"/>
     </row>
     <row r="10" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B10" s="169"/>
-      <c r="C10" s="173"/>
-      <c r="D10" s="174"/>
-      <c r="E10" s="174"/>
-      <c r="F10" s="175"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="88"/>
       <c r="G10" s="19"/>
       <c r="H10" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="130"/>
-      <c r="J10" s="131"/>
+      <c r="I10" s="122"/>
+      <c r="J10" s="123"/>
     </row>
     <row r="11" spans="2:10" ht="16.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="175" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="127"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="128"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="125" t="s">
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="120"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="I11" s="133"/>
-      <c r="J11" s="134"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="126"/>
     </row>
     <row r="12" spans="2:10" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="2"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="132"/>
-      <c r="H12" s="126"/>
-      <c r="I12" s="135"/>
-      <c r="J12" s="136"/>
+      <c r="C12" s="121"/>
+      <c r="D12" s="121"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="97"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="128"/>
     </row>
     <row r="13" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B14" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="106"/>
-      <c r="D14" s="107"/>
-      <c r="E14" s="107"/>
-      <c r="F14" s="107"/>
-      <c r="G14" s="107"/>
-      <c r="H14" s="107"/>
-      <c r="I14" s="107"/>
-      <c r="J14" s="108"/>
+      <c r="C14" s="149"/>
+      <c r="D14" s="150"/>
+      <c r="E14" s="150"/>
+      <c r="F14" s="150"/>
+      <c r="G14" s="150"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="150"/>
+      <c r="J14" s="151"/>
     </row>
     <row r="15" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B15" s="71" t="s">
@@ -2192,174 +2194,174 @@
       <c r="D15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="93" t="s">
+      <c r="E15" s="101" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="94"/>
-      <c r="G15" s="93" t="s">
+      <c r="F15" s="137"/>
+      <c r="G15" s="101" t="s">
         <v>42</v>
       </c>
-      <c r="H15" s="109"/>
-      <c r="I15" s="109"/>
-      <c r="J15" s="110"/>
+      <c r="H15" s="102"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="103"/>
     </row>
     <row r="16" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="111"/>
-      <c r="D16" s="112"/>
-      <c r="E16" s="112"/>
-      <c r="F16" s="112"/>
-      <c r="G16" s="112"/>
-      <c r="H16" s="112"/>
-      <c r="I16" s="112"/>
-      <c r="J16" s="113"/>
+      <c r="C16" s="104"/>
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="105"/>
+      <c r="J16" s="106"/>
     </row>
     <row r="17" spans="2:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="140" t="s">
+      <c r="B17" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="114"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="116"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="108"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="109"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B18" s="141"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="119"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="110"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="111"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="112"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B19" s="141"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="118"/>
-      <c r="H19" s="118"/>
-      <c r="I19" s="118"/>
-      <c r="J19" s="119"/>
+      <c r="B19" s="96"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="111"/>
+      <c r="I19" s="111"/>
+      <c r="J19" s="112"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B20" s="141"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="118"/>
-      <c r="H20" s="118"/>
-      <c r="I20" s="118"/>
-      <c r="J20" s="119"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="111"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="112"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B21" s="141"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="118"/>
-      <c r="F21" s="118"/>
-      <c r="G21" s="118"/>
-      <c r="H21" s="118"/>
-      <c r="I21" s="118"/>
-      <c r="J21" s="119"/>
+      <c r="B21" s="96"/>
+      <c r="C21" s="110"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="111"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="112"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B22" s="141"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="118"/>
-      <c r="H22" s="118"/>
-      <c r="I22" s="118"/>
-      <c r="J22" s="119"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="111"/>
+      <c r="G22" s="111"/>
+      <c r="H22" s="111"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="112"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B23" s="141"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="118"/>
-      <c r="J23" s="119"/>
+      <c r="B23" s="96"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="111"/>
+      <c r="F23" s="111"/>
+      <c r="G23" s="111"/>
+      <c r="H23" s="111"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="112"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B24" s="141"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="118"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="118"/>
-      <c r="I24" s="118"/>
-      <c r="J24" s="119"/>
+      <c r="B24" s="96"/>
+      <c r="C24" s="110"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="111"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="111"/>
+      <c r="H24" s="111"/>
+      <c r="I24" s="111"/>
+      <c r="J24" s="112"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B25" s="141"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="118"/>
-      <c r="F25" s="118"/>
-      <c r="G25" s="118"/>
-      <c r="H25" s="118"/>
-      <c r="I25" s="118"/>
-      <c r="J25" s="119"/>
+      <c r="B25" s="96"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="111"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="111"/>
+      <c r="J25" s="112"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B26" s="141"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="118"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="118"/>
-      <c r="G26" s="118"/>
-      <c r="H26" s="118"/>
-      <c r="I26" s="118"/>
-      <c r="J26" s="119"/>
+      <c r="B26" s="96"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="111"/>
+      <c r="H26" s="111"/>
+      <c r="I26" s="111"/>
+      <c r="J26" s="112"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B27" s="141"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="118"/>
-      <c r="F27" s="118"/>
-      <c r="G27" s="118"/>
-      <c r="H27" s="118"/>
-      <c r="I27" s="118"/>
-      <c r="J27" s="119"/>
+      <c r="B27" s="96"/>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="111"/>
+      <c r="F27" s="111"/>
+      <c r="G27" s="111"/>
+      <c r="H27" s="111"/>
+      <c r="I27" s="111"/>
+      <c r="J27" s="112"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B28" s="141"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="118"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="118"/>
-      <c r="G28" s="118"/>
-      <c r="H28" s="118"/>
-      <c r="I28" s="118"/>
-      <c r="J28" s="119"/>
+      <c r="B28" s="96"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="111"/>
+      <c r="H28" s="111"/>
+      <c r="I28" s="111"/>
+      <c r="J28" s="112"/>
     </row>
     <row r="29" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="126"/>
-      <c r="C29" s="120"/>
-      <c r="D29" s="121"/>
-      <c r="E29" s="121"/>
-      <c r="F29" s="121"/>
-      <c r="G29" s="121"/>
-      <c r="H29" s="121"/>
-      <c r="I29" s="121"/>
-      <c r="J29" s="122"/>
+      <c r="B29" s="97"/>
+      <c r="C29" s="113"/>
+      <c r="D29" s="114"/>
+      <c r="E29" s="114"/>
+      <c r="F29" s="114"/>
+      <c r="G29" s="114"/>
+      <c r="H29" s="114"/>
+      <c r="I29" s="114"/>
+      <c r="J29" s="115"/>
     </row>
     <row r="30" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C30" s="23"/>
@@ -2382,36 +2384,36 @@
       <c r="D32" s="18"/>
     </row>
     <row r="33" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="75" t="s">
+      <c r="B33" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="98" t="s">
+      <c r="C33" s="141" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="99"/>
+      <c r="D33" s="142"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="100" t="s">
+      <c r="F33" s="143" t="s">
         <v>36</v>
       </c>
-      <c r="G33" s="101"/>
-      <c r="H33" s="137"/>
-      <c r="I33" s="138"/>
-      <c r="J33" s="139"/>
+      <c r="G33" s="144"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="93"/>
+      <c r="J33" s="94"/>
     </row>
     <row r="34" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="35" spans="2:10" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="9"/>
-      <c r="C35" s="95" t="s">
+      <c r="C35" s="138" t="s">
         <v>22</v>
       </c>
-      <c r="D35" s="96"/>
-      <c r="E35" s="97"/>
-      <c r="F35" s="102" t="s">
+      <c r="D35" s="139"/>
+      <c r="E35" s="140"/>
+      <c r="F35" s="145" t="s">
         <v>23</v>
       </c>
-      <c r="G35" s="103"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="104"/>
+      <c r="G35" s="146"/>
+      <c r="H35" s="146"/>
+      <c r="I35" s="147"/>
       <c r="J35" s="20" t="s">
         <v>24</v>
       </c>
@@ -2420,69 +2422,86 @@
       <c r="B36" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="90"/>
-      <c r="D36" s="91"/>
-      <c r="E36" s="92"/>
-      <c r="F36" s="90"/>
-      <c r="G36" s="91"/>
-      <c r="H36" s="91"/>
-      <c r="I36" s="92"/>
-      <c r="J36" s="79"/>
+      <c r="C36" s="89"/>
+      <c r="D36" s="90"/>
+      <c r="E36" s="91"/>
+      <c r="F36" s="89"/>
+      <c r="G36" s="90"/>
+      <c r="H36" s="90"/>
+      <c r="I36" s="91"/>
+      <c r="J36" s="78"/>
     </row>
     <row r="37" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B37" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="90"/>
-      <c r="D37" s="91"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="90"/>
-      <c r="G37" s="91"/>
-      <c r="H37" s="91"/>
-      <c r="I37" s="92"/>
-      <c r="J37" s="80"/>
+      <c r="C37" s="89"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="91"/>
+      <c r="F37" s="89"/>
+      <c r="G37" s="90"/>
+      <c r="H37" s="90"/>
+      <c r="I37" s="91"/>
+      <c r="J37" s="79"/>
     </row>
     <row r="38" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B38" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="90"/>
-      <c r="D38" s="91"/>
-      <c r="E38" s="92"/>
-      <c r="F38" s="90"/>
-      <c r="G38" s="91"/>
-      <c r="H38" s="91"/>
-      <c r="I38" s="92"/>
-      <c r="J38" s="80"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="90"/>
+      <c r="E38" s="91"/>
+      <c r="F38" s="89"/>
+      <c r="G38" s="90"/>
+      <c r="H38" s="90"/>
+      <c r="I38" s="91"/>
+      <c r="J38" s="79"/>
     </row>
     <row r="39" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B39" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="C39" s="142"/>
-      <c r="D39" s="143"/>
-      <c r="E39" s="144"/>
-      <c r="F39" s="90"/>
-      <c r="G39" s="91"/>
-      <c r="H39" s="91"/>
-      <c r="I39" s="92"/>
-      <c r="J39" s="79"/>
+      <c r="C39" s="98"/>
+      <c r="D39" s="99"/>
+      <c r="E39" s="100"/>
+      <c r="F39" s="89"/>
+      <c r="G39" s="90"/>
+      <c r="H39" s="90"/>
+      <c r="I39" s="91"/>
+      <c r="J39" s="78"/>
     </row>
     <row r="40" spans="2:10" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="87"/>
-      <c r="D40" s="88"/>
-      <c r="E40" s="89"/>
-      <c r="F40" s="82"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="84"/>
-      <c r="J40" s="81"/>
+      <c r="C40" s="134"/>
+      <c r="D40" s="135"/>
+      <c r="E40" s="136"/>
+      <c r="F40" s="129"/>
+      <c r="G40" s="130"/>
+      <c r="H40" s="130"/>
+      <c r="I40" s="131"/>
+      <c r="J40" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="I11:J12"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="D4:H4"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:F10"/>
     <mergeCell ref="F38:I38"/>
@@ -2499,23 +2518,6 @@
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="G11:G12"/>
-    <mergeCell ref="I11:J12"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="C14:J14"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.3" footer="0.3"/>
@@ -2548,30 +2550,30 @@
     </row>
     <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="14"/>
-      <c r="C2" s="85" t="s">
+      <c r="C2" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="85"/>
+      <c r="D2" s="132"/>
       <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="14"/>
-      <c r="C3" s="112" t="s">
+      <c r="C3" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="112"/>
-      <c r="E3" s="145" t="s">
+      <c r="D3" s="105"/>
+      <c r="E3" s="166" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="146"/>
+      <c r="F3" s="167"/>
     </row>
     <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="14"/>
-      <c r="C4" s="105" t="s">
+      <c r="C4" s="148" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
       <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
@@ -2584,20 +2586,20 @@
     </row>
     <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="7" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="173" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="155"/>
-      <c r="C7" s="76" t="s">
+      <c r="B7" s="174"/>
+      <c r="C7" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="77" t="s">
+      <c r="D7" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="77" t="s">
+      <c r="E7" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="78" t="s">
+      <c r="F7" s="77" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2612,7 +2614,7 @@
       <c r="F8" s="33"/>
     </row>
     <row r="9" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="147" t="s">
+      <c r="A9" s="168" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="12" t="s">
@@ -2632,7 +2634,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="148"/>
+      <c r="A10" s="169"/>
       <c r="B10" s="11" t="s">
         <v>6</v>
       </c>
@@ -2650,17 +2652,17 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="160" t="s">
+      <c r="A11" s="158" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="161"/>
+      <c r="B11" s="159"/>
       <c r="C11" s="34"/>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
       <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="158" t="s">
+      <c r="A12" s="156" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="12" t="s">
@@ -2680,7 +2682,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="159"/>
+      <c r="A13" s="157"/>
       <c r="B13" s="11" t="s">
         <v>9</v>
       </c>
@@ -2698,7 +2700,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="164" t="s">
+      <c r="A14" s="162" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -2718,7 +2720,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="165"/>
+      <c r="A15" s="163"/>
       <c r="B15" s="37" t="s">
         <v>32</v>
       </c>
@@ -2736,10 +2738,10 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="166" t="s">
+      <c r="A16" s="164" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="167"/>
+      <c r="B16" s="165"/>
       <c r="C16" s="28" t="s">
         <v>30</v>
       </c>
@@ -2754,10 +2756,10 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="149" t="s">
+      <c r="A17" s="170" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="162" t="s">
+      <c r="B17" s="160" t="s">
         <v>34</v>
       </c>
       <c r="C17" s="52" t="s">
@@ -2774,8 +2776,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="150"/>
-      <c r="B18" s="163"/>
+      <c r="A18" s="171"/>
+      <c r="B18" s="161"/>
       <c r="C18" s="55" t="s">
         <v>45</v>
       </c>
@@ -2790,7 +2792,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="150"/>
+      <c r="A19" s="171"/>
       <c r="B19" s="58" t="s">
         <v>50</v>
       </c>
@@ -2808,7 +2810,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="150"/>
+      <c r="A20" s="171"/>
       <c r="B20" s="62" t="s">
         <v>35</v>
       </c>
@@ -2826,7 +2828,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="150"/>
+      <c r="A21" s="171"/>
       <c r="B21" s="41" t="s">
         <v>55</v>
       </c>
@@ -2844,7 +2846,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="151"/>
+      <c r="A22" s="172"/>
       <c r="B22" s="42" t="s">
         <v>50</v>
       </c>
@@ -2880,10 +2882,10 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="156" t="s">
+      <c r="A24" s="154" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="157"/>
+      <c r="B24" s="155"/>
       <c r="C24" s="63"/>
       <c r="D24" s="64"/>
       <c r="E24" s="64"/>
@@ -2891,13 +2893,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:B16"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
@@ -2906,6 +2901,13 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
